--- a/product_surveys/027_religious_parenting_app_survey--product_surveys.xlsx
+++ b/product_surveys/027_religious_parenting_app_survey--product_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1114,8 +1114,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'parental_control'}</t>
+          <t>parental_control</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Parental Control'}</t>
+          <t>Parental Control</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'parenting_community'}</t>
+          <t>parenting_community</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Parenting Community'}</t>
+          <t>Parenting Community</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'prayer_reminders'}</t>
+          <t>prayer_reminders</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Prayer Reminders'}</t>
+          <t>Prayer Reminders</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'bible_studies'}</t>
+          <t>bible_studies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Bible Studies'}</t>
+          <t>Bible Studies</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'christian'}</t>
+          <t>christian</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Christian'}</t>
+          <t>Christian</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'catholic'}</t>
+          <t>catholic</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Catholic'}</t>
+          <t>Catholic</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'prefer_not_to_answer'}</t>
+          <t>prefer_not_to_answer</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Prefer Not to Answer'}</t>
+          <t>Prefer Not to Answer</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'less_than_hs'}</t>
+          <t>less_than_hs</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Less Than HS'}</t>
+          <t>Less Than HS</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'hs_grad'}</t>
+          <t>hs_grad</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'HS Grad'}</t>
+          <t>HS Grad</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'some_college'}</t>
+          <t>some_college</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Some College'}</t>
+          <t>Some College</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'some_college_grad'}</t>
+          <t>some_college_grad</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Some College Grad'}</t>
+          <t>Some College Grad</t>
         </is>
       </c>
     </row>
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'bachelor'}</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Bachelor'}</t>
+          <t>Bachelor</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'some_grad_school'}</t>
+          <t>some_grad_school</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Some Grad School'}</t>
+          <t>Some Grad School</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1517,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'grad_school'}</t>
+          <t>grad_school</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Grad School'}</t>
+          <t>Grad School</t>
         </is>
       </c>
     </row>
@@ -1534,12 +1534,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'master'}</t>
+          <t>master</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Master'}</t>
+          <t>Master</t>
         </is>
       </c>
     </row>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'doctor'}</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Doctor'}</t>
+          <t>Doctor</t>
         </is>
       </c>
     </row>
@@ -1568,12 +1568,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'working_full-time'}</t>
+          <t>working_full-time</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Working Full-time'}</t>
+          <t>Working Full-time</t>
         </is>
       </c>
     </row>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'working_part-time'}</t>
+          <t>working_part-time</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'Working Part-time'}</t>
+          <t>Working Part-time</t>
         </is>
       </c>
     </row>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'unemployed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'Unemployed'}</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'retired'}</t>
+          <t>retired</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Retired'}</t>
+          <t>Retired</t>
         </is>
       </c>
     </row>
@@ -1636,12 +1636,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'stay-at-home_parent'}</t>
+          <t>stay-at-home_parent</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'Stay-At-Home Parent'}</t>
+          <t>Stay-At-Home Parent</t>
         </is>
       </c>
     </row>
@@ -1653,12 +1653,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'single'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'Single'}</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -1670,12 +1670,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'married'}</t>
+          <t>married</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'Married'}</t>
+          <t>Married</t>
         </is>
       </c>
     </row>
@@ -1687,12 +1687,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'separated'}</t>
+          <t>separated</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'Separated'}</t>
+          <t>Separated</t>
         </is>
       </c>
     </row>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'divorced'}</t>
+          <t>divorced</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 'Divorced'}</t>
+          <t>Divorced</t>
         </is>
       </c>
     </row>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_'widowed'}</t>
+          <t>widowed</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': 'Widowed'}</t>
+          <t>Widowed</t>
         </is>
       </c>
     </row>
